--- a/Subanalýzy/Pokrytí frekvence 260702.xlsx
+++ b/Subanalýzy/Pokrytí frekvence 260702.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://msmtcr.sharepoint.com/sites/Analyticktvar2-KA4/Sdilene dokumenty/KA 4 - Vybudování datové základny/KA4 C Propojenost a systemizace získávání a ukládání dat národních a mezinárodních zjišťování/7. Datový model školy/Datový model – navazující analýzy/Validace PAM r-kových proměnných/Subanalýzy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{8D982A3D-A70E-42ED-AD20-D0501F280F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097BDEC3-2A7F-47CE-BC97-39B8082CE0AD}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{8D982A3D-A70E-42ED-AD20-D0501F280F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E2A1C9C-92F0-4343-9E22-0960882390C5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{9D9EBF39-4D7B-4771-9B9C-4EDD5DF1C5FE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D9EBF39-4D7B-4771-9B9C-4EDD5DF1C5FE}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="948">
   <si>
     <t>polozka_index</t>
   </si>
@@ -2925,12 +2925,24 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2945,7 +2957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2954,11 +2966,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3318,7 +3341,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>364</v>
       </c>
       <c r="B2" t="s">
@@ -3331,7 +3354,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>365</v>
       </c>
       <c r="B3" t="s">
@@ -3344,7 +3367,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>366</v>
       </c>
       <c r="B4" t="s">
@@ -3357,7 +3380,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
         <v>367</v>
       </c>
       <c r="B5" t="s">
@@ -3370,7 +3393,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
         <v>368</v>
       </c>
       <c r="B6" t="s">
@@ -3383,13 +3406,13 @@
       </c>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="2">
@@ -3403,13 +3426,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="2">
@@ -3423,13 +3446,13 @@
       </c>
     </row>
     <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="2">
@@ -3443,13 +3466,13 @@
       </c>
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="2">
@@ -3463,13 +3486,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="2">
@@ -3483,13 +3506,13 @@
       </c>
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="2">
@@ -3503,13 +3526,13 @@
       </c>
     </row>
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="2">
@@ -3523,7 +3546,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="5" t="s">
         <v>376</v>
       </c>
       <c r="B14" t="s">
@@ -3536,7 +3559,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="5" t="s">
         <v>377</v>
       </c>
       <c r="B15" t="s">
@@ -3549,7 +3572,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="5" t="s">
         <v>378</v>
       </c>
       <c r="B16" t="s">
@@ -3562,7 +3585,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="5" t="s">
         <v>379</v>
       </c>
       <c r="B17" t="s">
@@ -3575,7 +3598,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="5" t="s">
         <v>380</v>
       </c>
       <c r="B18" t="s">
@@ -3588,7 +3611,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="5" t="s">
         <v>381</v>
       </c>
       <c r="B19" t="s">
@@ -3601,7 +3624,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>382</v>
       </c>
       <c r="B20" t="s">
@@ -3614,7 +3637,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>383</v>
       </c>
       <c r="B21" t="s">
@@ -3627,7 +3650,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="5" t="s">
         <v>384</v>
       </c>
       <c r="B22" t="s">
@@ -3640,7 +3663,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="5" t="s">
         <v>385</v>
       </c>
       <c r="B23" t="s">
@@ -3653,7 +3676,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="5" t="s">
         <v>386</v>
       </c>
       <c r="B24" t="s">
@@ -3666,7 +3689,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="5" t="s">
         <v>387</v>
       </c>
       <c r="B25" t="s">
@@ -3679,7 +3702,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="5" t="s">
         <v>388</v>
       </c>
       <c r="B26" t="s">
@@ -3692,7 +3715,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="5" t="s">
         <v>389</v>
       </c>
       <c r="B27" t="s">
@@ -3705,7 +3728,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="5" t="s">
         <v>390</v>
       </c>
       <c r="B28" t="s">
@@ -3718,7 +3741,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="5" t="s">
         <v>391</v>
       </c>
       <c r="B29" t="s">
@@ -3731,7 +3754,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="5" t="s">
         <v>392</v>
       </c>
       <c r="B30" t="s">
@@ -3744,7 +3767,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="5" t="s">
         <v>393</v>
       </c>
       <c r="B31" t="s">
@@ -3757,7 +3780,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="5" t="s">
         <v>394</v>
       </c>
       <c r="B32" t="s">
@@ -3770,7 +3793,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="5" t="s">
         <v>395</v>
       </c>
       <c r="B33" t="s">
@@ -3783,7 +3806,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="5" t="s">
         <v>396</v>
       </c>
       <c r="B34" t="s">
@@ -3796,7 +3819,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="5" t="s">
         <v>397</v>
       </c>
       <c r="B35" t="s">
@@ -3809,7 +3832,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="5" t="s">
         <v>398</v>
       </c>
       <c r="B36" t="s">
@@ -3822,13 +3845,13 @@
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D37" s="2">
@@ -3842,7 +3865,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="5" t="s">
         <v>400</v>
       </c>
       <c r="B38" t="s">
@@ -3855,7 +3878,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="5" t="s">
         <v>401</v>
       </c>
       <c r="B39" t="s">
@@ -3868,7 +3891,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="5" t="s">
         <v>402</v>
       </c>
       <c r="B40" t="s">
@@ -3881,7 +3904,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="5" t="s">
         <v>403</v>
       </c>
       <c r="B41" t="s">
@@ -3894,7 +3917,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="5" t="s">
         <v>404</v>
       </c>
       <c r="B42" t="s">
@@ -3907,13 +3930,13 @@
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B43" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="2">
@@ -3927,13 +3950,13 @@
       </c>
     </row>
     <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="2">
@@ -3947,7 +3970,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="5" t="s">
         <v>407</v>
       </c>
       <c r="B45" t="s">
@@ -3960,7 +3983,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="5" t="s">
         <v>408</v>
       </c>
       <c r="B46" t="s">
@@ -3973,7 +3996,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="5" t="s">
         <v>409</v>
       </c>
       <c r="B47" t="s">
@@ -3986,13 +4009,13 @@
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="B48" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="2">
@@ -4006,13 +4029,13 @@
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B49" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B49" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="2">
@@ -4026,7 +4049,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="5" t="s">
         <v>412</v>
       </c>
       <c r="B50" t="s">
@@ -4039,7 +4062,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="5" t="s">
         <v>413</v>
       </c>
       <c r="B51" t="s">
@@ -4052,7 +4075,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="5" t="s">
         <v>414</v>
       </c>
       <c r="B52" t="s">
@@ -4065,7 +4088,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="5" t="s">
         <v>415</v>
       </c>
       <c r="B53" t="s">
@@ -4078,13 +4101,13 @@
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="B54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="2">
@@ -4098,13 +4121,13 @@
       </c>
     </row>
     <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D55" s="2">
@@ -4118,13 +4141,13 @@
       </c>
     </row>
     <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="B56" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B56" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D56" s="2">
@@ -4138,7 +4161,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="5" t="s">
         <v>419</v>
       </c>
       <c r="B57" t="s">
@@ -4151,7 +4174,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="5" t="s">
         <v>420</v>
       </c>
       <c r="B58" t="s">
@@ -4164,7 +4187,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="5" t="s">
         <v>421</v>
       </c>
       <c r="B59" t="s">
@@ -4177,13 +4200,13 @@
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B60" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B60" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D60" s="2">
@@ -4197,13 +4220,13 @@
       </c>
     </row>
     <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B61" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="B61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="2">
@@ -4217,7 +4240,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="5" t="s">
         <v>424</v>
       </c>
       <c r="B62" t="s">
@@ -4230,7 +4253,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="5" t="s">
         <v>425</v>
       </c>
       <c r="B63" t="s">
@@ -4243,7 +4266,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="5" t="s">
         <v>426</v>
       </c>
       <c r="B64" t="s">
@@ -4256,13 +4279,13 @@
       </c>
     </row>
     <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B65" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="B65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D65" s="2">
@@ -4276,7 +4299,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="5" t="s">
         <v>428</v>
       </c>
       <c r="B66" t="s">
@@ -4289,7 +4312,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="5" t="s">
         <v>429</v>
       </c>
       <c r="B67" t="s">
@@ -4302,7 +4325,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="5" t="s">
         <v>430</v>
       </c>
       <c r="B68" t="s">
@@ -4315,7 +4338,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="5" t="s">
         <v>431</v>
       </c>
       <c r="B69" t="s">
@@ -4328,7 +4351,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="5" t="s">
         <v>432</v>
       </c>
       <c r="B70" t="s">
@@ -4341,7 +4364,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="5" t="s">
         <v>433</v>
       </c>
       <c r="B71" t="s">
@@ -4354,13 +4377,13 @@
       </c>
     </row>
     <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="B72" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="B72" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="2">
@@ -4374,13 +4397,13 @@
       </c>
     </row>
     <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B73" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B73" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="2">
@@ -4394,7 +4417,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="5" t="s">
         <v>436</v>
       </c>
       <c r="B74" t="s">
@@ -4407,7 +4430,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="5" t="s">
         <v>437</v>
       </c>
       <c r="B75" t="s">
@@ -4420,13 +4443,13 @@
       </c>
     </row>
     <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="B76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="2">
@@ -4440,13 +4463,13 @@
       </c>
     </row>
     <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="B77" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B77" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="2">
@@ -4460,13 +4483,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="B78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="B78" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="2">
@@ -4480,13 +4503,13 @@
       </c>
     </row>
     <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="B79" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="B79" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="2">
@@ -4500,13 +4523,13 @@
       </c>
     </row>
     <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B80" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B80" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D80" s="2">
@@ -4520,13 +4543,13 @@
       </c>
     </row>
     <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="B81" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="B81" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="2">
@@ -4540,13 +4563,13 @@
       </c>
     </row>
     <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="B82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B82" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="2">
@@ -4560,13 +4583,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="B83" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="B83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="2">
@@ -4580,13 +4603,13 @@
       </c>
     </row>
     <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="B84" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="B84" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="2">
@@ -4600,13 +4623,13 @@
       </c>
     </row>
     <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="B85" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="2">
@@ -4620,13 +4643,13 @@
       </c>
     </row>
     <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="B86" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="B86" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="2">
@@ -4640,13 +4663,13 @@
       </c>
     </row>
     <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="B87" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="B87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D87" s="2">
@@ -4660,13 +4683,13 @@
       </c>
     </row>
     <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B88" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="B88" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="2">
@@ -4680,7 +4703,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="5" t="s">
         <v>451</v>
       </c>
       <c r="B89" t="s">
@@ -4693,13 +4716,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="B90" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="B90" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="2">
@@ -4713,13 +4736,13 @@
       </c>
     </row>
     <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="B91" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="B91" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D91" s="2">
@@ -4733,13 +4756,13 @@
       </c>
     </row>
     <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B92" t="s">
-        <v>11</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="B92" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D92" s="2">
@@ -4753,13 +4776,13 @@
       </c>
     </row>
     <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="B93" t="s">
-        <v>11</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="B93" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="2">
@@ -4773,13 +4796,13 @@
       </c>
     </row>
     <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="B94" t="s">
-        <v>11</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="B94" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="2">
@@ -4793,13 +4816,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="B95" t="s">
-        <v>11</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="B95" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D95" s="2">
@@ -4813,13 +4836,13 @@
       </c>
     </row>
     <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B96" t="s">
-        <v>11</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="B96" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D96" s="2">
@@ -4833,13 +4856,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="B97" t="s">
-        <v>11</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="B97" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D97" s="2">
@@ -4853,13 +4876,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="B98" t="s">
-        <v>11</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="B98" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="2">
@@ -4873,13 +4896,13 @@
       </c>
     </row>
     <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="B99" t="s">
-        <v>11</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="B99" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="2">
@@ -4893,13 +4916,13 @@
       </c>
     </row>
     <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B100" t="s">
-        <v>11</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="B100" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="2">
@@ -4913,13 +4936,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B101" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="B101" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="2">
@@ -4933,13 +4956,13 @@
       </c>
     </row>
     <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="B102" t="s">
-        <v>11</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="2">
@@ -4953,13 +4976,13 @@
       </c>
     </row>
     <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="B103" t="s">
-        <v>11</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="B103" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2">
@@ -4973,13 +4996,13 @@
       </c>
     </row>
     <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="B104" t="s">
-        <v>11</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="B104" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2">
@@ -4993,13 +5016,13 @@
       </c>
     </row>
     <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="B105" t="s">
-        <v>11</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="B105" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2">
@@ -5013,13 +5036,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="B106" t="s">
-        <v>11</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="B106" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D106" s="2">
@@ -5033,13 +5056,13 @@
       </c>
     </row>
     <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="B107" t="s">
-        <v>11</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="B107" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="2">
@@ -5053,13 +5076,13 @@
       </c>
     </row>
     <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="B108" t="s">
-        <v>11</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="B108" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="2">
@@ -5073,13 +5096,13 @@
       </c>
     </row>
     <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="B109" t="s">
-        <v>11</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="B109" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2">
@@ -5093,13 +5116,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="B110" t="s">
-        <v>11</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="B110" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="2">
@@ -5113,13 +5136,13 @@
       </c>
     </row>
     <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="B111" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="B111" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="2">
@@ -5133,13 +5156,13 @@
       </c>
     </row>
     <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="B112" t="s">
-        <v>11</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="B112" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="2">
@@ -5153,13 +5176,13 @@
       </c>
     </row>
     <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="B113" t="s">
-        <v>11</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="B113" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D113" s="2">
@@ -5173,13 +5196,13 @@
       </c>
     </row>
     <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B114" t="s">
-        <v>11</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="B114" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D114" s="2">
@@ -5193,13 +5216,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="B115" t="s">
-        <v>11</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="B115" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D115" s="2">
@@ -5213,13 +5236,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="B116" t="s">
-        <v>11</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="B116" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D116" s="2">
@@ -5233,13 +5256,13 @@
       </c>
     </row>
     <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B117" t="s">
-        <v>11</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B117" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D117" s="2">
@@ -5253,13 +5276,13 @@
       </c>
     </row>
     <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="A118" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="B118" t="s">
-        <v>11</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B118" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D118" s="2">
@@ -5273,13 +5296,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="A119" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="B119" t="s">
-        <v>11</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B119" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D119" s="2">
@@ -5293,13 +5316,13 @@
       </c>
     </row>
     <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="B120" t="s">
-        <v>11</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D120" s="2">
@@ -5313,13 +5336,13 @@
       </c>
     </row>
     <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B121" t="s">
-        <v>11</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="B121" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D121" s="2">
@@ -5333,13 +5356,13 @@
       </c>
     </row>
     <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="B122" t="s">
-        <v>11</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="B122" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D122" s="2">
@@ -5353,13 +5376,13 @@
       </c>
     </row>
     <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B123" t="s">
-        <v>11</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="B123" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D123" s="2">
@@ -5373,13 +5396,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="B124" t="s">
-        <v>11</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D124" s="2">
@@ -5393,13 +5416,13 @@
       </c>
     </row>
     <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="A125" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B125" t="s">
-        <v>11</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="B125" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D125" s="2">
@@ -5413,13 +5436,13 @@
       </c>
     </row>
     <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="A126" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="B126" t="s">
-        <v>11</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B126" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D126" s="2">
@@ -5433,13 +5456,13 @@
       </c>
     </row>
     <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B127" t="s">
-        <v>11</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="B127" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D127" s="2">
@@ -5453,13 +5476,13 @@
       </c>
     </row>
     <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="A128" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="B128" t="s">
-        <v>11</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="B128" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D128" s="2">
@@ -5473,13 +5496,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="B129" t="s">
-        <v>11</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="B129" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D129" s="2">
@@ -5493,13 +5516,13 @@
       </c>
     </row>
     <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="A130" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B130" t="s">
-        <v>11</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="B130" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D130" s="2">
@@ -5513,13 +5536,13 @@
       </c>
     </row>
     <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="A131" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="B131" t="s">
-        <v>11</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="B131" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D131" s="2">
@@ -5533,13 +5556,13 @@
       </c>
     </row>
     <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="A132" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="B132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B132" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="2">
@@ -5553,13 +5576,13 @@
       </c>
     </row>
     <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="A133" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="B133" t="s">
-        <v>11</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="B133" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="2">
@@ -5573,13 +5596,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="B134" t="s">
-        <v>11</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="B134" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="2">
@@ -5593,13 +5616,13 @@
       </c>
     </row>
     <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B135" t="s">
-        <v>11</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="B135" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="2">
@@ -5613,13 +5636,13 @@
       </c>
     </row>
     <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="A136" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="B136" t="s">
-        <v>11</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="B136" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="2">
@@ -5633,13 +5656,13 @@
       </c>
     </row>
     <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="A137" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="B137" t="s">
-        <v>11</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="B137" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="2">
@@ -5653,13 +5676,13 @@
       </c>
     </row>
     <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="A138" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="B138" t="s">
-        <v>11</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="B138" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="2">
@@ -5673,13 +5696,13 @@
       </c>
     </row>
     <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+      <c r="A139" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B139" t="s">
-        <v>11</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="B139" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D139" s="2">
@@ -5693,13 +5716,13 @@
       </c>
     </row>
     <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="A140" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B140" t="s">
-        <v>11</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="B140" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D140" s="2">
@@ -5713,13 +5736,13 @@
       </c>
     </row>
     <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="A141" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="B141" t="s">
-        <v>11</v>
-      </c>
-      <c r="C141" t="s">
+      <c r="B141" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D141" s="2">
@@ -5733,13 +5756,13 @@
       </c>
     </row>
     <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="A142" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="B142" t="s">
-        <v>11</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="B142" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D142" s="2">
@@ -5753,13 +5776,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+      <c r="A143" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B143" t="s">
-        <v>11</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="B143" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D143" s="2">
@@ -5773,13 +5796,13 @@
       </c>
     </row>
     <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+      <c r="A144" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B144" t="s">
-        <v>11</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="B144" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D144" s="2">
@@ -5793,13 +5816,13 @@
       </c>
     </row>
     <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+      <c r="A145" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="B145" t="s">
-        <v>11</v>
-      </c>
-      <c r="C145" t="s">
+      <c r="B145" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D145" s="2">
@@ -5813,13 +5836,13 @@
       </c>
     </row>
     <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+      <c r="A146" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="B146" t="s">
-        <v>11</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="B146" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D146" s="2">
@@ -5833,13 +5856,13 @@
       </c>
     </row>
     <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+      <c r="A147" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B147" t="s">
-        <v>11</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="B147" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D147" s="2">
@@ -5853,13 +5876,13 @@
       </c>
     </row>
     <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+      <c r="A148" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B148" t="s">
-        <v>11</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="B148" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D148" s="2">
@@ -5873,13 +5896,13 @@
       </c>
     </row>
     <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+      <c r="A149" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="B149" t="s">
-        <v>11</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="B149" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D149" s="2">
@@ -5893,13 +5916,13 @@
       </c>
     </row>
     <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+      <c r="A150" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="B150" t="s">
-        <v>11</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="B150" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D150" s="2">
@@ -5913,13 +5936,13 @@
       </c>
     </row>
     <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+      <c r="A151" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="B151" t="s">
-        <v>11</v>
-      </c>
-      <c r="C151" t="s">
+      <c r="B151" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D151" s="2">
@@ -5933,13 +5956,13 @@
       </c>
     </row>
     <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+      <c r="A152" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="B152" t="s">
-        <v>11</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="B152" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D152" s="2">
@@ -5953,13 +5976,13 @@
       </c>
     </row>
     <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+      <c r="A153" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="B153" t="s">
-        <v>11</v>
-      </c>
-      <c r="C153" t="s">
+      <c r="B153" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D153" s="2">
@@ -5973,13 +5996,13 @@
       </c>
     </row>
     <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+      <c r="A154" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B154" t="s">
-        <v>11</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="B154" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D154" s="2">
@@ -5993,13 +6016,13 @@
       </c>
     </row>
     <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="A155" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B155" t="s">
-        <v>11</v>
-      </c>
-      <c r="C155" t="s">
+      <c r="B155" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D155" s="2">
@@ -6013,13 +6036,13 @@
       </c>
     </row>
     <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="A156" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="B156" t="s">
-        <v>11</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="B156" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D156" s="2">
@@ -6033,13 +6056,13 @@
       </c>
     </row>
     <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="A157" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B157" t="s">
-        <v>11</v>
-      </c>
-      <c r="C157" t="s">
+      <c r="B157" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D157" s="2">
@@ -6053,7 +6076,7 @@
       </c>
     </row>
     <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="A158" s="5" t="s">
         <v>520</v>
       </c>
       <c r="B158" t="s">
@@ -6066,13 +6089,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="A159" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B159" t="s">
-        <v>11</v>
-      </c>
-      <c r="C159" t="s">
+      <c r="B159" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D159" s="2">
@@ -6086,13 +6109,13 @@
       </c>
     </row>
     <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+      <c r="A160" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="B160" t="s">
-        <v>11</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="B160" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D160" s="2">
@@ -6106,13 +6129,13 @@
       </c>
     </row>
     <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+      <c r="A161" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="B161" t="s">
-        <v>11</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="B161" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D161" s="2">
@@ -6126,13 +6149,13 @@
       </c>
     </row>
     <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+      <c r="A162" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B162" t="s">
-        <v>11</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="B162" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D162" s="2">
@@ -6146,13 +6169,13 @@
       </c>
     </row>
     <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+      <c r="A163" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B163" t="s">
-        <v>11</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="B163" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D163" s="2">
@@ -6166,13 +6189,13 @@
       </c>
     </row>
     <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+      <c r="A164" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="B164" t="s">
-        <v>11</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="B164" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D164" s="2">
@@ -6186,13 +6209,13 @@
       </c>
     </row>
     <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+      <c r="A165" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="B165" t="s">
-        <v>11</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="B165" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D165" s="2">
@@ -6206,13 +6229,13 @@
       </c>
     </row>
     <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+      <c r="A166" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="B166" t="s">
-        <v>11</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="B166" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D166" s="2">
@@ -6226,13 +6249,13 @@
       </c>
     </row>
     <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+      <c r="A167" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="B167" t="s">
-        <v>11</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="B167" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D167" s="2">
@@ -6246,13 +6269,13 @@
       </c>
     </row>
     <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+      <c r="A168" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="B168" t="s">
-        <v>11</v>
-      </c>
-      <c r="C168" t="s">
+      <c r="B168" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D168" s="2">
@@ -6266,13 +6289,13 @@
       </c>
     </row>
     <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+      <c r="A169" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="B169" t="s">
-        <v>11</v>
-      </c>
-      <c r="C169" t="s">
+      <c r="B169" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D169" s="2">
@@ -6286,7 +6309,7 @@
       </c>
     </row>
     <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+      <c r="A170" s="5" t="s">
         <v>532</v>
       </c>
       <c r="B170" t="s">
@@ -6299,7 +6322,7 @@
       </c>
     </row>
     <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+      <c r="A171" s="5" t="s">
         <v>533</v>
       </c>
       <c r="B171" t="s">
@@ -6312,7 +6335,7 @@
       </c>
     </row>
     <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+      <c r="A172" s="5" t="s">
         <v>534</v>
       </c>
       <c r="B172" t="s">
@@ -6325,7 +6348,7 @@
       </c>
     </row>
     <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+      <c r="A173" s="5" t="s">
         <v>535</v>
       </c>
       <c r="B173" t="s">
@@ -6338,13 +6361,13 @@
       </c>
     </row>
     <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+      <c r="A174" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="B174" t="s">
-        <v>11</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="B174" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D174" s="2">
@@ -6358,13 +6381,13 @@
       </c>
     </row>
     <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+      <c r="A175" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="B175" t="s">
-        <v>11</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="B175" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D175" s="2">
@@ -6378,13 +6401,13 @@
       </c>
     </row>
     <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+      <c r="A176" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="B176" t="s">
-        <v>11</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="B176" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D176" s="2">
@@ -6398,13 +6421,13 @@
       </c>
     </row>
     <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+      <c r="A177" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B177" t="s">
-        <v>11</v>
-      </c>
-      <c r="C177" t="s">
+      <c r="B177" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D177" s="2">
@@ -6418,13 +6441,13 @@
       </c>
     </row>
     <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
+      <c r="A178" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B178" t="s">
-        <v>11</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="B178" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D178" s="2">
@@ -6438,7 +6461,7 @@
       </c>
     </row>
     <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
+      <c r="A179" s="5" t="s">
         <v>541</v>
       </c>
       <c r="B179" t="s">
@@ -6451,13 +6474,13 @@
       </c>
     </row>
     <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
+      <c r="A180" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="B180" t="s">
-        <v>11</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="B180" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D180" s="2">
@@ -6471,13 +6494,13 @@
       </c>
     </row>
     <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
+      <c r="A181" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B181" t="s">
-        <v>11</v>
-      </c>
-      <c r="C181" t="s">
+      <c r="B181" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D181" s="2">
@@ -6491,7 +6514,7 @@
       </c>
     </row>
     <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
+      <c r="A182" s="5" t="s">
         <v>544</v>
       </c>
       <c r="B182" t="s">
@@ -6504,7 +6527,7 @@
       </c>
     </row>
     <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
+      <c r="A183" s="5" t="s">
         <v>545</v>
       </c>
       <c r="B183" t="s">
@@ -6517,7 +6540,7 @@
       </c>
     </row>
     <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
+      <c r="A184" s="5" t="s">
         <v>546</v>
       </c>
       <c r="B184" t="s">
@@ -6530,7 +6553,7 @@
       </c>
     </row>
     <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
+      <c r="A185" s="5" t="s">
         <v>547</v>
       </c>
       <c r="B185" t="s">
@@ -6543,7 +6566,7 @@
       </c>
     </row>
     <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
+      <c r="A186" s="5" t="s">
         <v>548</v>
       </c>
       <c r="B186" t="s">
@@ -6556,7 +6579,7 @@
       </c>
     </row>
     <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
+      <c r="A187" s="5" t="s">
         <v>549</v>
       </c>
       <c r="B187" t="s">
@@ -6569,13 +6592,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
+      <c r="A188" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="B188" t="s">
-        <v>11</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="B188" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D188" s="2">
@@ -6589,13 +6612,13 @@
       </c>
     </row>
     <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
+      <c r="A189" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="B189" t="s">
-        <v>11</v>
-      </c>
-      <c r="C189" t="s">
+      <c r="B189" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D189" s="2">
@@ -6609,13 +6632,13 @@
       </c>
     </row>
     <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
+      <c r="A190" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="B190" t="s">
-        <v>11</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="B190" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D190" s="2">
@@ -6629,13 +6652,13 @@
       </c>
     </row>
     <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
+      <c r="A191" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="B191" t="s">
-        <v>11</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="B191" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D191" s="2">
@@ -6649,13 +6672,13 @@
       </c>
     </row>
     <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
+      <c r="A192" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="B192" t="s">
-        <v>11</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="B192" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D192" s="2">
@@ -6669,13 +6692,13 @@
       </c>
     </row>
     <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
+      <c r="A193" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="B193" t="s">
-        <v>11</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="B193" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D193" s="2">
@@ -6689,13 +6712,13 @@
       </c>
     </row>
     <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
+      <c r="A194" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="B194" t="s">
-        <v>11</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="B194" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D194" s="2">
@@ -6709,13 +6732,13 @@
       </c>
     </row>
     <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
+      <c r="A195" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="B195" t="s">
-        <v>11</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="B195" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D195" s="2">
@@ -6729,13 +6752,13 @@
       </c>
     </row>
     <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
+      <c r="A196" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="B196" t="s">
-        <v>11</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="B196" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D196" s="2">
@@ -6749,13 +6772,13 @@
       </c>
     </row>
     <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
+      <c r="A197" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="B197" t="s">
-        <v>11</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="B197" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D197" s="2">
@@ -6769,13 +6792,13 @@
       </c>
     </row>
     <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
+      <c r="A198" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="B198" t="s">
-        <v>11</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="B198" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D198" s="2">
@@ -6789,13 +6812,13 @@
       </c>
     </row>
     <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
+      <c r="A199" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="B199" t="s">
-        <v>11</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="B199" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D199" s="2">
@@ -6809,13 +6832,13 @@
       </c>
     </row>
     <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
+      <c r="A200" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="B200" t="s">
-        <v>11</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="B200" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D200" s="2">
@@ -6829,13 +6852,13 @@
       </c>
     </row>
     <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
+      <c r="A201" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="B201" t="s">
-        <v>11</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="B201" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D201" s="2">
@@ -6849,13 +6872,13 @@
       </c>
     </row>
     <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
+      <c r="A202" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="B202" t="s">
-        <v>11</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="B202" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D202" s="2">
@@ -6869,13 +6892,13 @@
       </c>
     </row>
     <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
+      <c r="A203" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="B203" t="s">
-        <v>11</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="B203" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D203" s="2">
@@ -6889,13 +6912,13 @@
       </c>
     </row>
     <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
+      <c r="A204" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="B204" t="s">
-        <v>11</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="B204" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D204" s="2">
@@ -6909,13 +6932,13 @@
       </c>
     </row>
     <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
+      <c r="A205" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="B205" t="s">
-        <v>11</v>
-      </c>
-      <c r="C205" t="s">
+      <c r="B205" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D205" s="2">
@@ -6929,7 +6952,7 @@
       </c>
     </row>
     <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
+      <c r="A206" s="5" t="s">
         <v>568</v>
       </c>
       <c r="B206" t="s">
@@ -6942,7 +6965,7 @@
       </c>
     </row>
     <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
+      <c r="A207" s="5" t="s">
         <v>569</v>
       </c>
       <c r="B207" t="s">
@@ -6955,7 +6978,7 @@
       </c>
     </row>
     <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
+      <c r="A208" s="5" t="s">
         <v>570</v>
       </c>
       <c r="B208" t="s">
@@ -6968,7 +6991,7 @@
       </c>
     </row>
     <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
+      <c r="A209" s="5" t="s">
         <v>571</v>
       </c>
       <c r="B209" t="s">
@@ -6981,7 +7004,7 @@
       </c>
     </row>
     <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
+      <c r="A210" s="5" t="s">
         <v>572</v>
       </c>
       <c r="B210" t="s">
@@ -6994,7 +7017,7 @@
       </c>
     </row>
     <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
+      <c r="A211" s="5" t="s">
         <v>573</v>
       </c>
       <c r="B211" t="s">
@@ -7007,7 +7030,7 @@
       </c>
     </row>
     <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
+      <c r="A212" s="5" t="s">
         <v>574</v>
       </c>
       <c r="B212" t="s">
@@ -7020,7 +7043,7 @@
       </c>
     </row>
     <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
+      <c r="A213" s="5" t="s">
         <v>575</v>
       </c>
       <c r="B213" t="s">
@@ -7033,7 +7056,7 @@
       </c>
     </row>
     <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
+      <c r="A214" s="5" t="s">
         <v>576</v>
       </c>
       <c r="B214" t="s">
@@ -7046,7 +7069,7 @@
       </c>
     </row>
     <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
+      <c r="A215" s="5" t="s">
         <v>577</v>
       </c>
       <c r="B215" t="s">
@@ -7059,7 +7082,7 @@
       </c>
     </row>
     <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
+      <c r="A216" s="5" t="s">
         <v>578</v>
       </c>
       <c r="B216" t="s">
@@ -7072,7 +7095,7 @@
       </c>
     </row>
     <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
+      <c r="A217" s="5" t="s">
         <v>579</v>
       </c>
       <c r="B217" t="s">
@@ -7085,7 +7108,7 @@
       </c>
     </row>
     <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
+      <c r="A218" s="5" t="s">
         <v>580</v>
       </c>
       <c r="B218" t="s">
@@ -7098,7 +7121,7 @@
       </c>
     </row>
     <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
+      <c r="A219" s="5" t="s">
         <v>581</v>
       </c>
       <c r="B219" t="s">
@@ -7111,7 +7134,7 @@
       </c>
     </row>
     <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
+      <c r="A220" s="5" t="s">
         <v>582</v>
       </c>
       <c r="B220" t="s">
@@ -7124,7 +7147,7 @@
       </c>
     </row>
     <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
+      <c r="A221" s="5" t="s">
         <v>583</v>
       </c>
       <c r="B221" t="s">
@@ -7137,7 +7160,7 @@
       </c>
     </row>
     <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
+      <c r="A222" s="5" t="s">
         <v>584</v>
       </c>
       <c r="B222" t="s">
@@ -7150,7 +7173,7 @@
       </c>
     </row>
     <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
+      <c r="A223" s="5" t="s">
         <v>585</v>
       </c>
       <c r="B223" t="s">
@@ -7163,7 +7186,7 @@
       </c>
     </row>
     <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
+      <c r="A224" s="5" t="s">
         <v>586</v>
       </c>
       <c r="B224" t="s">
@@ -7176,7 +7199,7 @@
       </c>
     </row>
     <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
+      <c r="A225" s="5" t="s">
         <v>587</v>
       </c>
       <c r="B225" t="s">
@@ -7189,7 +7212,7 @@
       </c>
     </row>
     <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
+      <c r="A226" s="5" t="s">
         <v>588</v>
       </c>
       <c r="B226" t="s">
@@ -7202,7 +7225,7 @@
       </c>
     </row>
     <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
+      <c r="A227" s="5" t="s">
         <v>589</v>
       </c>
       <c r="B227" t="s">
@@ -7215,7 +7238,7 @@
       </c>
     </row>
     <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
+      <c r="A228" s="5" t="s">
         <v>590</v>
       </c>
       <c r="B228" t="s">
@@ -7228,7 +7251,7 @@
       </c>
     </row>
     <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
+      <c r="A229" s="5" t="s">
         <v>591</v>
       </c>
       <c r="B229" t="s">
@@ -7241,7 +7264,7 @@
       </c>
     </row>
     <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
+      <c r="A230" s="5" t="s">
         <v>592</v>
       </c>
       <c r="B230" t="s">
@@ -7254,7 +7277,7 @@
       </c>
     </row>
     <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
+      <c r="A231" s="5" t="s">
         <v>593</v>
       </c>
       <c r="B231" t="s">
@@ -7267,7 +7290,7 @@
       </c>
     </row>
     <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
+      <c r="A232" s="5" t="s">
         <v>594</v>
       </c>
       <c r="B232" t="s">
@@ -7280,7 +7303,7 @@
       </c>
     </row>
     <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
+      <c r="A233" s="5" t="s">
         <v>595</v>
       </c>
       <c r="B233" t="s">
@@ -7293,7 +7316,7 @@
       </c>
     </row>
     <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
+      <c r="A234" s="5" t="s">
         <v>596</v>
       </c>
       <c r="B234" t="s">
@@ -7306,7 +7329,7 @@
       </c>
     </row>
     <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
+      <c r="A235" s="5" t="s">
         <v>597</v>
       </c>
       <c r="B235" t="s">
@@ -7319,7 +7342,7 @@
       </c>
     </row>
     <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
+      <c r="A236" s="5" t="s">
         <v>598</v>
       </c>
       <c r="B236" t="s">
@@ -7332,7 +7355,7 @@
       </c>
     </row>
     <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
+      <c r="A237" s="5" t="s">
         <v>599</v>
       </c>
       <c r="B237" t="s">
@@ -7345,7 +7368,7 @@
       </c>
     </row>
     <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
+      <c r="A238" s="5" t="s">
         <v>600</v>
       </c>
       <c r="B238" t="s">
@@ -7358,7 +7381,7 @@
       </c>
     </row>
     <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
+      <c r="A239" s="5" t="s">
         <v>601</v>
       </c>
       <c r="B239" t="s">
@@ -7371,7 +7394,7 @@
       </c>
     </row>
     <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
+      <c r="A240" s="5" t="s">
         <v>602</v>
       </c>
       <c r="B240" t="s">
@@ -7384,7 +7407,7 @@
       </c>
     </row>
     <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
+      <c r="A241" s="5" t="s">
         <v>603</v>
       </c>
       <c r="B241" t="s">
@@ -7397,7 +7420,7 @@
       </c>
     </row>
     <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
+      <c r="A242" s="5" t="s">
         <v>604</v>
       </c>
       <c r="B242" t="s">
@@ -7410,7 +7433,7 @@
       </c>
     </row>
     <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
+      <c r="A243" s="5" t="s">
         <v>605</v>
       </c>
       <c r="B243" t="s">
@@ -7423,7 +7446,7 @@
       </c>
     </row>
     <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
+      <c r="A244" s="5" t="s">
         <v>606</v>
       </c>
       <c r="B244" t="s">
@@ -7436,7 +7459,7 @@
       </c>
     </row>
     <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
+      <c r="A245" s="5" t="s">
         <v>607</v>
       </c>
       <c r="B245" t="s">
@@ -7449,7 +7472,7 @@
       </c>
     </row>
     <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
+      <c r="A246" s="5" t="s">
         <v>608</v>
       </c>
       <c r="B246" t="s">
@@ -7462,7 +7485,7 @@
       </c>
     </row>
     <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
+      <c r="A247" s="5" t="s">
         <v>609</v>
       </c>
       <c r="B247" t="s">
@@ -7475,13 +7498,13 @@
       </c>
     </row>
     <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
+      <c r="A248" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="B248" t="s">
-        <v>11</v>
-      </c>
-      <c r="C248" t="s">
+      <c r="B248" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D248" s="2">
@@ -7495,13 +7518,13 @@
       </c>
     </row>
     <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
+      <c r="A249" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="B249" t="s">
-        <v>11</v>
-      </c>
-      <c r="C249" t="s">
+      <c r="B249" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D249" s="2">
@@ -7515,13 +7538,13 @@
       </c>
     </row>
     <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
+      <c r="A250" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="B250" t="s">
-        <v>11</v>
-      </c>
-      <c r="C250" t="s">
+      <c r="B250" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D250" s="2">
@@ -7535,13 +7558,13 @@
       </c>
     </row>
     <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
+      <c r="A251" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="B251" t="s">
-        <v>11</v>
-      </c>
-      <c r="C251" t="s">
+      <c r="B251" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D251" s="2">
@@ -7555,13 +7578,13 @@
       </c>
     </row>
     <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
+      <c r="A252" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="B252" t="s">
-        <v>11</v>
-      </c>
-      <c r="C252" t="s">
+      <c r="B252" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D252" s="2">
@@ -7575,13 +7598,13 @@
       </c>
     </row>
     <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
+      <c r="A253" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="B253" t="s">
-        <v>11</v>
-      </c>
-      <c r="C253" t="s">
+      <c r="B253" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D253" s="2">
@@ -7595,13 +7618,13 @@
       </c>
     </row>
     <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
+      <c r="A254" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="B254" t="s">
-        <v>11</v>
-      </c>
-      <c r="C254" t="s">
+      <c r="B254" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D254" s="2">
@@ -7615,7 +7638,7 @@
       </c>
     </row>
     <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
+      <c r="A255" s="5" t="s">
         <v>617</v>
       </c>
       <c r="B255" t="s">
@@ -7628,7 +7651,7 @@
       </c>
     </row>
     <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
+      <c r="A256" s="5" t="s">
         <v>618</v>
       </c>
       <c r="B256" t="s">
@@ -7641,7 +7664,7 @@
       </c>
     </row>
     <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
+      <c r="A257" s="5" t="s">
         <v>619</v>
       </c>
       <c r="B257" t="s">
@@ -7654,7 +7677,7 @@
       </c>
     </row>
     <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
+      <c r="A258" s="5" t="s">
         <v>620</v>
       </c>
       <c r="B258" t="s">
@@ -7667,13 +7690,13 @@
       </c>
     </row>
     <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
+      <c r="A259" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="B259" t="s">
-        <v>11</v>
-      </c>
-      <c r="C259" t="s">
+      <c r="B259" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D259" s="2">
@@ -7687,13 +7710,13 @@
       </c>
     </row>
     <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
+      <c r="A260" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="B260" t="s">
-        <v>11</v>
-      </c>
-      <c r="C260" t="s">
+      <c r="B260" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D260" s="2">
@@ -7707,13 +7730,13 @@
       </c>
     </row>
     <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
+      <c r="A261" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="B261" t="s">
-        <v>11</v>
-      </c>
-      <c r="C261" t="s">
+      <c r="B261" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D261" s="2">
@@ -7727,13 +7750,13 @@
       </c>
     </row>
     <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
+      <c r="A262" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="B262" t="s">
-        <v>11</v>
-      </c>
-      <c r="C262" t="s">
+      <c r="B262" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D262" s="2">
@@ -7747,13 +7770,13 @@
       </c>
     </row>
     <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
+      <c r="A263" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="B263" t="s">
-        <v>11</v>
-      </c>
-      <c r="C263" t="s">
+      <c r="B263" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D263" s="2">
@@ -7767,13 +7790,13 @@
       </c>
     </row>
     <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
+      <c r="A264" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="B264" t="s">
-        <v>11</v>
-      </c>
-      <c r="C264" t="s">
+      <c r="B264" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D264" s="2">
@@ -7787,13 +7810,13 @@
       </c>
     </row>
     <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A265" t="s">
+      <c r="A265" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="B265" t="s">
-        <v>11</v>
-      </c>
-      <c r="C265" t="s">
+      <c r="B265" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D265" s="2">
@@ -7807,7 +7830,7 @@
       </c>
     </row>
     <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
+      <c r="A266" s="5" t="s">
         <v>628</v>
       </c>
       <c r="B266" t="s">
@@ -7820,13 +7843,13 @@
       </c>
     </row>
     <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
+      <c r="A267" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="B267" t="s">
-        <v>11</v>
-      </c>
-      <c r="C267" t="s">
+      <c r="B267" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D267" s="2">
@@ -7840,7 +7863,7 @@
       </c>
     </row>
     <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
+      <c r="A268" s="5" t="s">
         <v>630</v>
       </c>
       <c r="B268" t="s">
@@ -7853,7 +7876,7 @@
       </c>
     </row>
     <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
+      <c r="A269" s="5" t="s">
         <v>631</v>
       </c>
       <c r="B269" t="s">
@@ -7866,7 +7889,7 @@
       </c>
     </row>
     <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
+      <c r="A270" s="5" t="s">
         <v>632</v>
       </c>
       <c r="B270" t="s">
@@ -7879,13 +7902,13 @@
       </c>
     </row>
     <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
+      <c r="A271" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="B271" t="s">
-        <v>11</v>
-      </c>
-      <c r="C271" t="s">
+      <c r="B271" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C271" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D271" s="2">
@@ -7899,13 +7922,13 @@
       </c>
     </row>
     <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
+      <c r="A272" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="B272" t="s">
-        <v>11</v>
-      </c>
-      <c r="C272" t="s">
+      <c r="B272" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C272" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D272" s="2">
@@ -7919,13 +7942,13 @@
       </c>
     </row>
     <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
+      <c r="A273" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="B273" t="s">
-        <v>11</v>
-      </c>
-      <c r="C273" t="s">
+      <c r="B273" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D273" s="2">
@@ -7939,13 +7962,13 @@
       </c>
     </row>
     <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
+      <c r="A274" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="B274" t="s">
-        <v>11</v>
-      </c>
-      <c r="C274" t="s">
+      <c r="B274" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D274" s="2">
@@ -7959,13 +7982,13 @@
       </c>
     </row>
     <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
+      <c r="A275" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="B275" t="s">
-        <v>11</v>
-      </c>
-      <c r="C275" t="s">
+      <c r="B275" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D275" s="2">
@@ -7979,13 +8002,13 @@
       </c>
     </row>
     <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
+      <c r="A276" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="B276" t="s">
-        <v>11</v>
-      </c>
-      <c r="C276" t="s">
+      <c r="B276" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C276" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D276" s="2">
@@ -7999,13 +8022,13 @@
       </c>
     </row>
     <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
+      <c r="A277" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="B277" t="s">
-        <v>11</v>
-      </c>
-      <c r="C277" t="s">
+      <c r="B277" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D277" s="2">
@@ -8019,13 +8042,13 @@
       </c>
     </row>
     <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
+      <c r="A278" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="B278" t="s">
-        <v>11</v>
-      </c>
-      <c r="C278" t="s">
+      <c r="B278" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C278" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D278" s="2">
@@ -8039,7 +8062,7 @@
       </c>
     </row>
     <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
+      <c r="A279" s="5" t="s">
         <v>641</v>
       </c>
       <c r="B279" t="s">
@@ -8052,13 +8075,13 @@
       </c>
     </row>
     <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
+      <c r="A280" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="B280" t="s">
-        <v>11</v>
-      </c>
-      <c r="C280" t="s">
+      <c r="B280" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C280" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D280" s="2">
@@ -8072,13 +8095,13 @@
       </c>
     </row>
     <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
+      <c r="A281" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="B281" t="s">
-        <v>11</v>
-      </c>
-      <c r="C281" t="s">
+      <c r="B281" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C281" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D281" s="2">
@@ -8092,13 +8115,13 @@
       </c>
     </row>
     <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
+      <c r="A282" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="B282" t="s">
-        <v>11</v>
-      </c>
-      <c r="C282" t="s">
+      <c r="B282" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C282" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D282" s="2">
@@ -8112,13 +8135,13 @@
       </c>
     </row>
     <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
+      <c r="A283" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="B283" t="s">
-        <v>11</v>
-      </c>
-      <c r="C283" t="s">
+      <c r="B283" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D283" s="2">
@@ -8132,13 +8155,13 @@
       </c>
     </row>
     <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
+      <c r="A284" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="B284" t="s">
-        <v>11</v>
-      </c>
-      <c r="C284" t="s">
+      <c r="B284" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C284" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D284" s="2">
@@ -8152,13 +8175,13 @@
       </c>
     </row>
     <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
+      <c r="A285" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="B285" t="s">
-        <v>11</v>
-      </c>
-      <c r="C285" t="s">
+      <c r="B285" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C285" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D285" s="2">
@@ -8172,13 +8195,13 @@
       </c>
     </row>
     <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
+      <c r="A286" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="B286" t="s">
-        <v>11</v>
-      </c>
-      <c r="C286" t="s">
+      <c r="B286" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C286" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D286" s="2">
@@ -8192,13 +8215,13 @@
       </c>
     </row>
     <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
+      <c r="A287" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="B287" t="s">
-        <v>11</v>
-      </c>
-      <c r="C287" t="s">
+      <c r="B287" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C287" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D287" s="2">
@@ -8212,13 +8235,13 @@
       </c>
     </row>
     <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
+      <c r="A288" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B288" t="s">
-        <v>11</v>
-      </c>
-      <c r="C288" t="s">
+      <c r="B288" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C288" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D288" s="2">
@@ -8232,13 +8255,13 @@
       </c>
     </row>
     <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
+      <c r="A289" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="B289" t="s">
-        <v>11</v>
-      </c>
-      <c r="C289" t="s">
+      <c r="B289" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C289" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D289" s="2">
@@ -8252,13 +8275,13 @@
       </c>
     </row>
     <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
+      <c r="A290" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="B290" t="s">
-        <v>11</v>
-      </c>
-      <c r="C290" t="s">
+      <c r="B290" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C290" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D290" s="2">
@@ -8272,13 +8295,13 @@
       </c>
     </row>
     <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
+      <c r="A291" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="B291" t="s">
-        <v>11</v>
-      </c>
-      <c r="C291" t="s">
+      <c r="B291" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C291" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D291" s="2">
@@ -8292,13 +8315,13 @@
       </c>
     </row>
     <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
+      <c r="A292" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="B292" t="s">
-        <v>11</v>
-      </c>
-      <c r="C292" t="s">
+      <c r="B292" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C292" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D292" s="2">
@@ -8312,13 +8335,13 @@
       </c>
     </row>
     <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
+      <c r="A293" s="5" t="s">
         <v>655</v>
       </c>
-      <c r="B293" t="s">
-        <v>11</v>
-      </c>
-      <c r="C293" t="s">
+      <c r="B293" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C293" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D293" s="2">
@@ -8332,13 +8355,13 @@
       </c>
     </row>
     <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
+      <c r="A294" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="B294" t="s">
-        <v>11</v>
-      </c>
-      <c r="C294" t="s">
+      <c r="B294" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C294" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D294" s="2">
@@ -8352,13 +8375,13 @@
       </c>
     </row>
     <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
+      <c r="A295" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="B295" t="s">
-        <v>11</v>
-      </c>
-      <c r="C295" t="s">
+      <c r="B295" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C295" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D295" s="2">
@@ -8372,13 +8395,13 @@
       </c>
     </row>
     <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
+      <c r="A296" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="B296" t="s">
-        <v>11</v>
-      </c>
-      <c r="C296" t="s">
+      <c r="B296" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C296" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D296" s="2">
@@ -8392,13 +8415,13 @@
       </c>
     </row>
     <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
+      <c r="A297" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="B297" t="s">
-        <v>11</v>
-      </c>
-      <c r="C297" t="s">
+      <c r="B297" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D297" s="2">
@@ -8412,13 +8435,13 @@
       </c>
     </row>
     <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
+      <c r="A298" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="B298" t="s">
-        <v>11</v>
-      </c>
-      <c r="C298" t="s">
+      <c r="B298" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C298" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D298" s="2">
@@ -8432,13 +8455,13 @@
       </c>
     </row>
     <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
+      <c r="A299" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="B299" t="s">
-        <v>11</v>
-      </c>
-      <c r="C299" t="s">
+      <c r="B299" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C299" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D299" s="2">
@@ -8452,13 +8475,13 @@
       </c>
     </row>
     <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
+      <c r="A300" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="B300" t="s">
-        <v>11</v>
-      </c>
-      <c r="C300" t="s">
+      <c r="B300" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D300" s="2">
@@ -8472,13 +8495,13 @@
       </c>
     </row>
     <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
+      <c r="A301" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="B301" t="s">
-        <v>11</v>
-      </c>
-      <c r="C301" t="s">
+      <c r="B301" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D301" s="2">
@@ -8492,13 +8515,13 @@
       </c>
     </row>
     <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
+      <c r="A302" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="B302" t="s">
-        <v>11</v>
-      </c>
-      <c r="C302" t="s">
+      <c r="B302" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C302" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D302" s="2">
@@ -8512,13 +8535,13 @@
       </c>
     </row>
     <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
+      <c r="A303" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="B303" t="s">
-        <v>11</v>
-      </c>
-      <c r="C303" t="s">
+      <c r="B303" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C303" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D303" s="2">
@@ -8532,13 +8555,13 @@
       </c>
     </row>
     <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
+      <c r="A304" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="B304" t="s">
-        <v>11</v>
-      </c>
-      <c r="C304" t="s">
+      <c r="B304" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C304" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D304" s="2">
@@ -8552,13 +8575,13 @@
       </c>
     </row>
     <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
+      <c r="A305" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="B305" t="s">
-        <v>11</v>
-      </c>
-      <c r="C305" t="s">
+      <c r="B305" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C305" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D305" s="2">
@@ -8572,13 +8595,13 @@
       </c>
     </row>
     <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
+      <c r="A306" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="B306" t="s">
-        <v>11</v>
-      </c>
-      <c r="C306" t="s">
+      <c r="B306" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C306" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D306" s="2">
@@ -8592,13 +8615,13 @@
       </c>
     </row>
     <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
+      <c r="A307" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="B307" t="s">
-        <v>11</v>
-      </c>
-      <c r="C307" t="s">
+      <c r="B307" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C307" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D307" s="2">
@@ -8612,13 +8635,13 @@
       </c>
     </row>
     <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
+      <c r="A308" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="B308" t="s">
-        <v>11</v>
-      </c>
-      <c r="C308" t="s">
+      <c r="B308" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C308" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D308" s="2">
@@ -8632,13 +8655,13 @@
       </c>
     </row>
     <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
+      <c r="A309" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="B309" t="s">
-        <v>11</v>
-      </c>
-      <c r="C309" t="s">
+      <c r="B309" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C309" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D309" s="2">
@@ -8652,13 +8675,13 @@
       </c>
     </row>
     <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
+      <c r="A310" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="B310" t="s">
-        <v>11</v>
-      </c>
-      <c r="C310" t="s">
+      <c r="B310" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C310" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D310" s="2">
@@ -8672,13 +8695,13 @@
       </c>
     </row>
     <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
+      <c r="A311" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="B311" t="s">
-        <v>11</v>
-      </c>
-      <c r="C311" t="s">
+      <c r="B311" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C311" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D311" s="2">
@@ -8692,13 +8715,13 @@
       </c>
     </row>
     <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
+      <c r="A312" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="B312" t="s">
-        <v>11</v>
-      </c>
-      <c r="C312" t="s">
+      <c r="B312" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C312" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D312" s="2">
@@ -8712,13 +8735,13 @@
       </c>
     </row>
     <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
+      <c r="A313" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="B313" t="s">
-        <v>11</v>
-      </c>
-      <c r="C313" t="s">
+      <c r="B313" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C313" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D313" s="2">
@@ -8732,13 +8755,13 @@
       </c>
     </row>
     <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A314" t="s">
+      <c r="A314" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="B314" t="s">
-        <v>11</v>
-      </c>
-      <c r="C314" t="s">
+      <c r="B314" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C314" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D314" s="2">
@@ -8752,13 +8775,13 @@
       </c>
     </row>
     <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
+      <c r="A315" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="B315" t="s">
-        <v>11</v>
-      </c>
-      <c r="C315" t="s">
+      <c r="B315" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C315" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D315" s="2">
@@ -8772,13 +8795,13 @@
       </c>
     </row>
     <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
+      <c r="A316" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="B316" t="s">
-        <v>11</v>
-      </c>
-      <c r="C316" t="s">
+      <c r="B316" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C316" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D316" s="2">
@@ -8792,13 +8815,13 @@
       </c>
     </row>
     <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
+      <c r="A317" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="B317" t="s">
-        <v>11</v>
-      </c>
-      <c r="C317" t="s">
+      <c r="B317" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C317" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D317" s="2">
@@ -8812,13 +8835,13 @@
       </c>
     </row>
     <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
+      <c r="A318" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="B318" t="s">
-        <v>11</v>
-      </c>
-      <c r="C318" t="s">
+      <c r="B318" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D318" s="2">
@@ -8832,13 +8855,13 @@
       </c>
     </row>
     <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A319" t="s">
+      <c r="A319" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="B319" t="s">
-        <v>11</v>
-      </c>
-      <c r="C319" t="s">
+      <c r="B319" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C319" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D319" s="2">
@@ -8852,13 +8875,13 @@
       </c>
     </row>
     <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
+      <c r="A320" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="B320" t="s">
-        <v>11</v>
-      </c>
-      <c r="C320" t="s">
+      <c r="B320" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C320" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D320" s="2">
@@ -8872,13 +8895,13 @@
       </c>
     </row>
     <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
+      <c r="A321" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B321" t="s">
-        <v>11</v>
-      </c>
-      <c r="C321" t="s">
+      <c r="B321" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C321" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D321" s="2">
@@ -8892,13 +8915,13 @@
       </c>
     </row>
     <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A322" t="s">
+      <c r="A322" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="B322" t="s">
-        <v>11</v>
-      </c>
-      <c r="C322" t="s">
+      <c r="B322" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C322" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D322" s="2">
@@ -8912,13 +8935,13 @@
       </c>
     </row>
     <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
+      <c r="A323" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="B323" t="s">
-        <v>11</v>
-      </c>
-      <c r="C323" t="s">
+      <c r="B323" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C323" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D323" s="2">
@@ -8932,13 +8955,13 @@
       </c>
     </row>
     <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
+      <c r="A324" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="B324" t="s">
-        <v>11</v>
-      </c>
-      <c r="C324" t="s">
+      <c r="B324" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C324" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D324" s="2">
@@ -8952,13 +8975,13 @@
       </c>
     </row>
     <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A325" t="s">
+      <c r="A325" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="B325" t="s">
-        <v>11</v>
-      </c>
-      <c r="C325" t="s">
+      <c r="B325" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C325" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D325" s="2">
@@ -8972,7 +8995,7 @@
       </c>
     </row>
     <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
+      <c r="A326" s="5" t="s">
         <v>688</v>
       </c>
       <c r="B326" t="s">
@@ -8985,7 +9008,7 @@
       </c>
     </row>
     <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
+      <c r="A327" s="5" t="s">
         <v>689</v>
       </c>
       <c r="B327" t="s">
@@ -8998,7 +9021,7 @@
       </c>
     </row>
     <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A328" t="s">
+      <c r="A328" s="5" t="s">
         <v>690</v>
       </c>
       <c r="B328" t="s">
@@ -9011,13 +9034,13 @@
       </c>
     </row>
     <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A329" t="s">
+      <c r="A329" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="B329" t="s">
-        <v>11</v>
-      </c>
-      <c r="C329" t="s">
+      <c r="B329" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C329" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D329" s="2">
@@ -9031,13 +9054,13 @@
       </c>
     </row>
     <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A330" t="s">
+      <c r="A330" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="B330" t="s">
-        <v>11</v>
-      </c>
-      <c r="C330" t="s">
+      <c r="B330" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C330" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D330" s="2">
@@ -9051,13 +9074,13 @@
       </c>
     </row>
     <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A331" t="s">
+      <c r="A331" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="B331" t="s">
-        <v>11</v>
-      </c>
-      <c r="C331" t="s">
+      <c r="B331" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C331" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D331" s="2">
@@ -9071,13 +9094,13 @@
       </c>
     </row>
     <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A332" t="s">
+      <c r="A332" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="B332" t="s">
-        <v>11</v>
-      </c>
-      <c r="C332" t="s">
+      <c r="B332" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C332" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D332" s="2">
@@ -9091,13 +9114,13 @@
       </c>
     </row>
     <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A333" t="s">
+      <c r="A333" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="B333" t="s">
-        <v>11</v>
-      </c>
-      <c r="C333" t="s">
+      <c r="B333" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C333" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D333" s="2">
@@ -9111,13 +9134,13 @@
       </c>
     </row>
     <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A334" t="s">
+      <c r="A334" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="B334" t="s">
-        <v>11</v>
-      </c>
-      <c r="C334" t="s">
+      <c r="B334" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C334" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D334" s="2">
@@ -9131,13 +9154,13 @@
       </c>
     </row>
     <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A335" t="s">
+      <c r="A335" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="B335" t="s">
-        <v>11</v>
-      </c>
-      <c r="C335" t="s">
+      <c r="B335" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C335" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D335" s="2">
@@ -9151,13 +9174,13 @@
       </c>
     </row>
     <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A336" t="s">
+      <c r="A336" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="B336" t="s">
-        <v>11</v>
-      </c>
-      <c r="C336" t="s">
+      <c r="B336" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C336" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D336" s="2">
@@ -9171,13 +9194,13 @@
       </c>
     </row>
     <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A337" t="s">
+      <c r="A337" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="B337" t="s">
-        <v>11</v>
-      </c>
-      <c r="C337" t="s">
+      <c r="B337" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C337" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D337" s="2">
@@ -9191,7 +9214,7 @@
       </c>
     </row>
     <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
+      <c r="A338" s="5" t="s">
         <v>700</v>
       </c>
       <c r="B338" t="s">
@@ -9204,7 +9227,7 @@
       </c>
     </row>
     <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A339" t="s">
+      <c r="A339" s="5" t="s">
         <v>701</v>
       </c>
       <c r="B339" t="s">
@@ -9217,7 +9240,7 @@
       </c>
     </row>
     <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
+      <c r="A340" s="5" t="s">
         <v>702</v>
       </c>
       <c r="B340" t="s">
@@ -9230,7 +9253,7 @@
       </c>
     </row>
     <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A341" t="s">
+      <c r="A341" s="5" t="s">
         <v>703</v>
       </c>
       <c r="B341" t="s">
@@ -9243,7 +9266,7 @@
       </c>
     </row>
     <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
+      <c r="A342" s="5" t="s">
         <v>704</v>
       </c>
       <c r="B342" t="s">
@@ -9256,13 +9279,13 @@
       </c>
     </row>
     <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A343" t="s">
+      <c r="A343" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="B343" t="s">
-        <v>11</v>
-      </c>
-      <c r="C343" t="s">
+      <c r="B343" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C343" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D343" s="2">
@@ -9276,13 +9299,13 @@
       </c>
     </row>
     <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
+      <c r="A344" s="5" t="s">
         <v>706</v>
       </c>
-      <c r="B344" t="s">
-        <v>11</v>
-      </c>
-      <c r="C344" t="s">
+      <c r="B344" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C344" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D344" s="2">
@@ -9296,13 +9319,13 @@
       </c>
     </row>
     <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
+      <c r="A345" s="5" t="s">
         <v>707</v>
       </c>
-      <c r="B345" t="s">
-        <v>11</v>
-      </c>
-      <c r="C345" t="s">
+      <c r="B345" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C345" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D345" s="2">
@@ -9316,13 +9339,13 @@
       </c>
     </row>
     <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
+      <c r="A346" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="B346" t="s">
-        <v>11</v>
-      </c>
-      <c r="C346" t="s">
+      <c r="B346" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C346" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D346" s="2">
@@ -9336,13 +9359,13 @@
       </c>
     </row>
     <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
+      <c r="A347" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="B347" t="s">
-        <v>11</v>
-      </c>
-      <c r="C347" t="s">
+      <c r="B347" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C347" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D347" s="2">
@@ -9356,13 +9379,13 @@
       </c>
     </row>
     <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
+      <c r="A348" s="5" t="s">
         <v>710</v>
       </c>
-      <c r="B348" t="s">
-        <v>11</v>
-      </c>
-      <c r="C348" t="s">
+      <c r="B348" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C348" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D348" s="2">
@@ -9376,13 +9399,13 @@
       </c>
     </row>
     <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
+      <c r="A349" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="B349" t="s">
-        <v>11</v>
-      </c>
-      <c r="C349" t="s">
+      <c r="B349" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C349" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D349" s="2">
@@ -9396,13 +9419,13 @@
       </c>
     </row>
     <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
+      <c r="A350" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="B350" t="s">
-        <v>11</v>
-      </c>
-      <c r="C350" t="s">
+      <c r="B350" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C350" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D350" s="2">
@@ -9416,13 +9439,13 @@
       </c>
     </row>
     <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A351" t="s">
+      <c r="A351" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="B351" t="s">
-        <v>11</v>
-      </c>
-      <c r="C351" t="s">
+      <c r="B351" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C351" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D351" s="2">
@@ -9436,13 +9459,13 @@
       </c>
     </row>
     <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A352" t="s">
+      <c r="A352" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="B352" t="s">
-        <v>11</v>
-      </c>
-      <c r="C352" t="s">
+      <c r="B352" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C352" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D352" s="2">
@@ -9456,13 +9479,13 @@
       </c>
     </row>
     <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A353" t="s">
+      <c r="A353" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="B353" t="s">
-        <v>11</v>
-      </c>
-      <c r="C353" t="s">
+      <c r="B353" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C353" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D353" s="2">
@@ -9476,13 +9499,13 @@
       </c>
     </row>
     <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A354" t="s">
+      <c r="A354" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="B354" t="s">
-        <v>11</v>
-      </c>
-      <c r="C354" t="s">
+      <c r="B354" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C354" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D354" s="2">
@@ -9496,13 +9519,13 @@
       </c>
     </row>
     <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A355" t="s">
+      <c r="A355" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="B355" t="s">
-        <v>11</v>
-      </c>
-      <c r="C355" t="s">
+      <c r="B355" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C355" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D355" s="2">
@@ -9516,13 +9539,13 @@
       </c>
     </row>
     <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A356" t="s">
+      <c r="A356" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="B356" t="s">
-        <v>11</v>
-      </c>
-      <c r="C356" t="s">
+      <c r="B356" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C356" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D356" s="2">
@@ -9536,13 +9559,13 @@
       </c>
     </row>
     <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A357" t="s">
+      <c r="A357" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="B357" t="s">
-        <v>11</v>
-      </c>
-      <c r="C357" t="s">
+      <c r="B357" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C357" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D357" s="2">
@@ -9556,13 +9579,13 @@
       </c>
     </row>
     <row r="358" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
+      <c r="A358" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="B358" t="s">
-        <v>11</v>
-      </c>
-      <c r="C358" t="s">
+      <c r="B358" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C358" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D358" s="2">
@@ -9576,13 +9599,13 @@
       </c>
     </row>
     <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A359" t="s">
+      <c r="A359" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="B359" t="s">
-        <v>11</v>
-      </c>
-      <c r="C359" t="s">
+      <c r="B359" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C359" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D359" s="2">
@@ -9596,13 +9619,13 @@
       </c>
     </row>
     <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A360" t="s">
+      <c r="A360" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="B360" t="s">
-        <v>11</v>
-      </c>
-      <c r="C360" t="s">
+      <c r="B360" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C360" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D360" s="2">
@@ -9616,13 +9639,13 @@
       </c>
     </row>
     <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A361" t="s">
+      <c r="A361" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="B361" t="s">
-        <v>11</v>
-      </c>
-      <c r="C361" t="s">
+      <c r="B361" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C361" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D361" s="2">
@@ -11641,15 +11664,15 @@
         <v>335</v>
       </c>
     </row>
-    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A505" t="s">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A505" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B505" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C505" t="s">
-        <v>336</v>
+      <c r="C505" s="4">
+        <v>3.12</v>
       </c>
       <c r="D505" s="2">
         <v>0.5</v>
@@ -11661,14 +11684,14 @@
         <v>337</v>
       </c>
     </row>
-    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A506" t="s">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A506" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="B506" t="s">
+      <c r="B506" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C506" t="s">
+      <c r="C506" s="4" t="s">
         <v>336</v>
       </c>
       <c r="D506" s="2">
@@ -11681,14 +11704,14 @@
         <v>338</v>
       </c>
     </row>
-    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A507" t="s">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A507" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="B507" t="s">
+      <c r="B507" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C507" t="s">
+      <c r="C507" s="4" t="s">
         <v>336</v>
       </c>
       <c r="D507" s="2">
@@ -11701,14 +11724,14 @@
         <v>339</v>
       </c>
     </row>
-    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A508" t="s">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A508" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="B508" t="s">
+      <c r="B508" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C508" t="s">
+      <c r="C508" s="4" t="s">
         <v>336</v>
       </c>
       <c r="D508" s="2">
@@ -11722,13 +11745,13 @@
       </c>
     </row>
     <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A509" t="s">
+      <c r="A509" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="B509" t="s">
-        <v>11</v>
-      </c>
-      <c r="C509" t="s">
+      <c r="B509" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C509" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D509" s="2">
@@ -11742,13 +11765,13 @@
       </c>
     </row>
     <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A510" t="s">
+      <c r="A510" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="B510" t="s">
-        <v>11</v>
-      </c>
-      <c r="C510" t="s">
+      <c r="B510" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C510" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D510" s="2">
@@ -11762,13 +11785,13 @@
       </c>
     </row>
     <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A511" t="s">
+      <c r="A511" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="B511" t="s">
-        <v>11</v>
-      </c>
-      <c r="C511" t="s">
+      <c r="B511" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C511" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D511" s="2">
@@ -11782,13 +11805,13 @@
       </c>
     </row>
     <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A512" t="s">
+      <c r="A512" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="B512" t="s">
-        <v>11</v>
-      </c>
-      <c r="C512" t="s">
+      <c r="B512" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C512" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D512" s="2">
@@ -12168,47 +12191,47 @@
       <c r="D540" s="2"/>
       <c r="E540" s="2"/>
     </row>
-    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A541" t="s">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A541" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="B541" t="s">
+      <c r="B541" s="4" t="s">
         <v>903</v>
       </c>
       <c r="F541" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A542" t="s">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A542" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="B542" t="s">
+      <c r="B542" s="4" t="s">
         <v>903</v>
       </c>
       <c r="F542" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A543" t="s">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A543" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="B543" t="s">
+      <c r="B543" s="4" t="s">
         <v>903</v>
       </c>
       <c r="F543" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A544" t="s">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A544" s="5" t="s">
         <v>929</v>
       </c>
-      <c r="B544" t="s">
-        <v>11</v>
-      </c>
-      <c r="C544" t="s">
+      <c r="B544" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C544" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D544" s="2">
@@ -12221,14 +12244,14 @@
         <v>910</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A545" t="s">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A545" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="B545" t="s">
-        <v>11</v>
-      </c>
-      <c r="C545" t="s">
+      <c r="B545" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C545" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D545" s="2">
@@ -12241,14 +12264,14 @@
         <v>911</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A546" t="s">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A546" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="B546" t="s">
-        <v>11</v>
-      </c>
-      <c r="C546" t="s">
+      <c r="B546" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C546" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D546" s="2">
@@ -12261,14 +12284,14 @@
         <v>912</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A547" t="s">
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A547" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="B547" t="s">
-        <v>11</v>
-      </c>
-      <c r="C547" t="s">
+      <c r="B547" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C547" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D547" s="2">
@@ -12281,14 +12304,14 @@
         <v>913</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A548" t="s">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A548" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="B548" t="s">
-        <v>11</v>
-      </c>
-      <c r="C548" t="s">
+      <c r="B548" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C548" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D548" s="2">
@@ -12301,14 +12324,14 @@
         <v>914</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A549" t="s">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A549" s="5" t="s">
         <v>934</v>
       </c>
-      <c r="B549" t="s">
-        <v>11</v>
-      </c>
-      <c r="C549" t="s">
+      <c r="B549" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C549" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D549" s="2">
@@ -12321,14 +12344,14 @@
         <v>915</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A550" t="s">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A550" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="B550" t="s">
-        <v>11</v>
-      </c>
-      <c r="C550" t="s">
+      <c r="B550" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C550" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D550" s="2">
@@ -12341,14 +12364,14 @@
         <v>916</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A551" t="s">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A551" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="B551" t="s">
-        <v>11</v>
-      </c>
-      <c r="C551" t="s">
+      <c r="B551" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C551" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D551" s="2">
@@ -12361,14 +12384,14 @@
         <v>917</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A552" t="s">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A552" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="B552" t="s">
-        <v>11</v>
-      </c>
-      <c r="C552" t="s">
+      <c r="B552" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C552" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D552" s="2">
@@ -12381,14 +12404,14 @@
         <v>918</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A553" t="s">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A553" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="B553" t="s">
-        <v>11</v>
-      </c>
-      <c r="C553" t="s">
+      <c r="B553" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C553" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D553" s="2">
@@ -12401,14 +12424,14 @@
         <v>919</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A554" t="s">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A554" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="B554" t="s">
-        <v>11</v>
-      </c>
-      <c r="C554" t="s">
+      <c r="B554" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C554" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D554" s="2">
@@ -12421,14 +12444,14 @@
         <v>920</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A555" t="s">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A555" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="B555" t="s">
-        <v>11</v>
-      </c>
-      <c r="C555" t="s">
+      <c r="B555" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C555" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D555" s="2">
@@ -12441,14 +12464,14 @@
         <v>921</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A556" t="s">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A556" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="B556" t="s">
-        <v>11</v>
-      </c>
-      <c r="C556" t="s">
+      <c r="B556" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C556" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D556" s="2">
@@ -12461,14 +12484,14 @@
         <v>922</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A557" t="s">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A557" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="B557" t="s">
-        <v>11</v>
-      </c>
-      <c r="C557" t="s">
+      <c r="B557" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C557" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D557" s="2">
@@ -12481,14 +12504,14 @@
         <v>923</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A558" t="s">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A558" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="B558" t="s">
-        <v>11</v>
-      </c>
-      <c r="C558" t="s">
+      <c r="B558" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C558" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D558" s="2">
@@ -12501,14 +12524,14 @@
         <v>924</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A559" t="s">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A559" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="B559" t="s">
-        <v>11</v>
-      </c>
-      <c r="C559" t="s">
+      <c r="B559" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C559" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D559" s="2">
@@ -12521,14 +12544,14 @@
         <v>925</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A560" t="s">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A560" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="B560" t="s">
-        <v>11</v>
-      </c>
-      <c r="C560" t="s">
+      <c r="B560" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C560" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D560" s="2">
@@ -12541,14 +12564,14 @@
         <v>926</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A561" t="s">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A561" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="B561" t="s">
-        <v>11</v>
-      </c>
-      <c r="C561" t="s">
+      <c r="B561" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C561" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D561" s="2">
@@ -12561,14 +12584,14 @@
         <v>927</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A562" t="s">
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A562" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="B562" t="s">
-        <v>11</v>
-      </c>
-      <c r="C562" t="s">
+      <c r="B562" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C562" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D562" s="2">
@@ -12584,27 +12607,7 @@
   </sheetData>
   <autoFilter ref="A1:F562" xr:uid="{703F5F7A-5AD3-4747-8D04-4248B8FF7633}">
     <filterColumn colId="0">
-      <filters>
-        <filter val="r02001.p1"/>
-        <filter val="r02002.p1"/>
-        <filter val="r02003.p1"/>
-        <filter val="r02004.p1"/>
-        <filter val="r02005.p1"/>
-        <filter val="r02006.p1"/>
-        <filter val="r02007.p1"/>
-        <filter val="r03072.p1"/>
-        <filter val="r03073.p1"/>
-        <filter val="r03074.p1"/>
-        <filter val="r03075.p1"/>
-        <filter val="r03076.p1"/>
-        <filter val="r03077.p1"/>
-        <filter val="r03078.p1"/>
-        <filter val="r03079.p1"/>
-        <filter val="r03080.p1"/>
-        <filter val="r03081.p1"/>
-        <filter val="r05018.p1"/>
-        <filter val="r05019.p1"/>
-      </filters>
+      <colorFilter dxfId="0"/>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
